--- a/Thesis Forecasting/metadata/random_forest/validation_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/random_forest/validation_average_metrics.xlsx
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.52859002181966</v>
+        <v>3.386005159095108</v>
       </c>
       <c r="E2" t="n">
-        <v>1.739151711725675</v>
+        <v>1.678480657713253</v>
       </c>
       <c r="F2" t="n">
-        <v>2.807124889541247</v>
+        <v>2.675410175200322</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9263963672885636</v>
+        <v>0.9331415154238221</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
-        <v>2.197333539992933</v>
+        <v>1.346888884370499</v>
       </c>
       <c r="E3" t="n">
-        <v>2.144955981389472</v>
+        <v>1.234468312569503</v>
       </c>
       <c r="F3" t="n">
-        <v>4.534518648274945</v>
+        <v>4.150251280106098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8014621728253392</v>
+        <v>0.8336856723563233</v>
       </c>
     </row>
     <row r="4">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D4" t="n">
-        <v>1.774556659412656</v>
+        <v>1.226140381658184</v>
       </c>
       <c r="E4" t="n">
-        <v>1.456443027139064</v>
+        <v>1.100333454368979</v>
       </c>
       <c r="F4" t="n">
-        <v>3.980111616750163</v>
+        <v>3.26922366793582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9338717637429117</v>
+        <v>0.9553845060592133</v>
       </c>
     </row>
     <row r="5">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D5" t="n">
-        <v>4.181556633756847</v>
+        <v>3.964092083803105</v>
       </c>
       <c r="E5" t="n">
-        <v>1.491315664584439</v>
+        <v>1.415609857474836</v>
       </c>
       <c r="F5" t="n">
-        <v>2.224479677726016</v>
+        <v>2.12653277869198</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049217652560917</v>
+        <v>0.9131102820191399</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.967630624280723</v>
+        <v>2.464661547382927</v>
       </c>
       <c r="E6" t="n">
-        <v>4.534963565508413</v>
+        <v>3.71714037173041</v>
       </c>
       <c r="F6" t="n">
-        <v>8.150774218763839</v>
+        <v>7.331512491350271</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8278085456100657</v>
+        <v>0.8606839906494381</v>
       </c>
     </row>
     <row r="7">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D7" t="n">
-        <v>4.182444181484814</v>
+        <v>3.730500739807862</v>
       </c>
       <c r="E7" t="n">
-        <v>1.343362405314368</v>
+        <v>1.197703904692743</v>
       </c>
       <c r="F7" t="n">
-        <v>2.089475624941428</v>
+        <v>1.955127140382782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8274916190187004</v>
+        <v>0.8489622213067463</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/random_forest/validation_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/random_forest/validation_average_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,37 +440,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
